--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:10</t>
+    <t xml:space="preserve">2026-09-09 23:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:04</t>
+    <t xml:space="preserve">2026-09-17 14:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:01</t>
+    <t xml:space="preserve">2026-09-23 12:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:31</t>
+    <t xml:space="preserve">2026-10-02 14:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_nuble.xlsx
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Yungay</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Chillán Viejo</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:22</t>
+    <t xml:space="preserve">2026-10-04 08:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:53</t>
+    <t xml:space="preserve">2026-10-05 10:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -544,7 +544,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>958912.12</v>
+        <v>958912.13</v>
       </c>
     </row>
     <row r="3">
@@ -595,7 +595,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>834095.62</v>
+        <v>834095.63</v>
       </c>
     </row>
     <row r="6">
@@ -629,7 +629,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>810547.12</v>
+        <v>810547.13</v>
       </c>
     </row>
     <row r="8">
